--- a/scripts/test-data/test-data-006-mockpass-import-demo.xlsx
+++ b/scripts/test-data/test-data-006-mockpass-import-demo.xlsx
@@ -460,12 +460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.996339" customWidth="1" style="4" min="1" max="1"/>
     <col width="14.282054" customWidth="1" style="4" min="2" max="2"/>
-    <col width="15.282054" customWidth="1" style="4" min="3" max="3"/>
+    <col width="42" customWidth="1" style="4" min="3" max="3"/>
     <col width="28.139196" customWidth="1" style="4" min="4" max="4"/>
     <col width="11.424911" customWidth="1" style="5" min="5" max="5"/>
     <col width="15.282054" customWidth="1" style="4" min="6" max="6"/>
@@ -494,70 +494,75 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>MockPassPersonId</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
           <t>IdentityNumber</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DateOfBirth</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>NationalityCode</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>CitizenshipStatusCode</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>StudentNumber</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>AcademicYear</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LevelCode</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>ClassCode</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>TemplateRow</t>
         </is>
@@ -570,61 +575,66 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>949ea5dd-8b01-5b53-8cf4-27d798b3012b</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
           <t>S7000121F</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Gideon Koh NUS</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>40152</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-121</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>NUS-S2-25</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.gideon.koh.nus.121@student.example.test</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+6591000121</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>121 Education Avenue, Singapore 100121</t>
         </is>
@@ -637,61 +647,66 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>55009235-cda5-580b-bbc9-cad2884539bd</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>S7000122G</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Hazel Ng NTU</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>37094</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-122</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>NTU-UG-25</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.hazel.ng.ntu.122@student.example.test</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+6591000122</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>122 Education Avenue, Singapore 100122</t>
         </is>
@@ -704,61 +719,66 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>a9124b9e-f269-51ee-820f-1fb8044510e6</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>S7000123H</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Isaac Chua SMU</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>35506</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-123</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>SMU-PG-25</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.isaac.chua.smu.123@student.example.test</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+6591000123</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>123 Education Avenue, Singapore 100123</t>
         </is>
@@ -771,61 +791,66 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>3fb3eeab-3990-5f30-afbe-11fac486763f</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>S7000124J</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Jia Min Seah SUTD</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>39730</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-124</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>SUTD-DR-25</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.jia.min.seah.sutd.124@student.example.test</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+6591000124</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>124 Education Avenue, Singapore 100124</t>
         </is>
@@ -838,61 +863,66 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>512d9f96-3693-55d2-b54b-8e3da435e6d1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>S7000125K</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Keira Low SIT</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>37729</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-125</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>SIT-UG-25</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.keira.low.sit.125@student.example.test</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+6591000125</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>125 Education Avenue, Singapore 100125</t>
         </is>
@@ -905,61 +935,66 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>7c40d485-44cd-5d61-b7db-b37fc2c15414</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>S7000126L</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Leon Ho NUS</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>36336</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-126</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>NUS-PG-26</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.leon.ho.nus.126@student.example.test</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+6591000126</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>126 Education Avenue, Singapore 100126</t>
         </is>
@@ -972,61 +1007,66 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>0e47a8e8-647a-564f-83f3-81ce2ffd57a1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>S7000127M</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Mira Das NTU</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>34676</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-127</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>NTU-DR-26</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.mira.das.ntu.127@student.example.test</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+6591000127</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>127 Education Avenue, Singapore 100127</t>
         </is>
@@ -1039,61 +1079,66 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>33fe9db2-a9d5-55d6-959b-2b98cf723b02</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>S7000128N</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Nolan Teo SMU</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>38797</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-128</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>SMU-S4-26</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.nolan.teo.smu.128@student.example.test</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+6591000128</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>128 Education Avenue, Singapore 100128</t>
         </is>
@@ -1106,61 +1151,66 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>b08920b8-4951-52e1-9c1e-80168b82dd92</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>S7000129P</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Olivia Chan SUTD</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>40309</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-129</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>SUTD-S3-26</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.olivia.chan.sutd.129@student.example.test</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+6591000129</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>129 Education Avenue, Singapore 100129</t>
         </is>
@@ -1173,61 +1223,66 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>261474ab-5504-574f-a0cf-6223b0460d3d</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>S7000130Q</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Pranav Menon SIT</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>36799</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-130</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>SIT-P6-26</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.pranav.menon.sit.130@student.example.test</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+6591000130</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>130 Education Avenue, Singapore 100130</t>
         </is>
@@ -1240,61 +1295,66 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>5ea5dba4-4dc8-5f09-8bb2-64d76b3be460</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>S7000131R</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Renee Yap NUS</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>35080</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-131</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>NUS-S2-27</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.renee.yap.nus.131@student.example.test</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+6591000131</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>131 Education Avenue, Singapore 100131</t>
         </is>
@@ -1307,61 +1367,66 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>960f999d-9c47-54bd-93bb-babed66eac60</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S7000132T</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Samuel Tay NTU</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>38175</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-132</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>NTU-UG-27</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.samuel.tay.ntu.132@student.example.test</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+6591000132</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>132 Education Avenue, Singapore 100132</t>
         </is>
@@ -1374,61 +1439,66 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>701469c0-4164-5602-999c-f48685155bb7</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>S7000133U</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Tara Nair SMU</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>39775</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-133</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>SMU-PG-27</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.tara.nair.smu.133@student.example.test</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+6591000133</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>133 Education Avenue, Singapore 100133</t>
         </is>
@@ -1441,61 +1511,66 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>d746e415-9a7c-5818-8b32-f5ab0975f2a9</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>S7000134V</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Vikram Singh SUTD</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>37531</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-134</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>SUTD-DR-27</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.vikram.singh.sutd.134@student.example.test</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+6591000134</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>134 Education Avenue, Singapore 100134</t>
         </is>
@@ -1508,61 +1583,66 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>401a69f0-9e66-5d18-86be-958da2f216d9</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>S7000135W</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Avery Tan SIT</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>38029</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-135</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>SIT-UG-27</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.avery.tan.sit.135@student.example.test</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+6591000135</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>135 Education Avenue, Singapore 100135</t>
         </is>
@@ -1575,61 +1655,66 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>b0add2a4-b969-583d-92fe-e23f7b3e98c7</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>S7000136X</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Bianca Lim NUS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>36010</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-136</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>NUS-PG-28</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.bianca.lim.nus.136@student.example.test</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+6591000136</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>136 Education Avenue, Singapore 100136</t>
         </is>
@@ -1642,61 +1727,66 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>8694ddbe-712a-533b-99c8-370caacfe5d5</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>S7000137Y</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Caleb Wong NTU</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>34292</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-137</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>NTU-DR-28</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.caleb.wong.ntu.137@student.example.test</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+6591000137</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>137 Education Avenue, Singapore 100137</t>
         </is>
@@ -1707,63 +1797,64 @@
       <c r="B19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>A7000138Z</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Daphne Lee SMU</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>38500</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-138</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>SMU-S4-28</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.daphne.lee.smu.138@student.example.test</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+6591000138</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>138 Education Avenue, Singapore 100138</t>
         </is>
@@ -1776,57 +1867,62 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>0786f78a-9b2f-509b-bd7a-c6d7d19989f1</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>S7000139A</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n">
         <v>39339</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-139</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>SUTD-S3-28</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.elias.goh.sutd.139@student.example.test</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+6591000139</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>139 Education Avenue, Singapore 100139</t>
         </is>
@@ -1839,61 +1935,66 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>6db73786-5aac-5682-aafe-c17fbaa88e18</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>S7000140B</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO006 Farah Rahman SIT</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>37287</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-140</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>SIT-P6-28</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>36922</v>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo006.farah.rahman.sit.140@student.example.test</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+6591000140</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>140 Education Avenue, Singapore 100140</t>
         </is>
